--- a/artfynd/S 1877-2020 artfynd.xlsx
+++ b/artfynd/S 1877-2020 artfynd.xlsx
@@ -1293,7 +1293,7 @@
         <v>136478486</v>
       </c>
       <c r="B7" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>136478488</v>
       </c>
       <c r="B8" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 1877-2020 artfynd.xlsx
+++ b/artfynd/S 1877-2020 artfynd.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Hammar, Hans Bucht</t>
+          <t>Hans Bucht, Karl Hammar</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Hammar, Hans Bucht</t>
+          <t>Hans Bucht, Karl Hammar</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/S 1877-2020 artfynd.xlsx
+++ b/artfynd/S 1877-2020 artfynd.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Bucht, Karl Hammar</t>
+          <t>Karl Hammar, Hans Bucht</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Bucht, Karl Hammar</t>
+          <t>Karl Hammar, Hans Bucht</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
